--- a/out/08_ISMS/SNX-ISMS-FRM-03 Supplier Technical Security Evaluation (Rev00 DRAFT).xlsx
+++ b/out/08_ISMS/SNX-ISMS-FRM-03 Supplier Technical Security Evaluation (Rev00 DRAFT).xlsx
@@ -15,8 +15,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kuesioner Keamanan" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Daftar'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Daftar Supplier'!$A$4:$L$52</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Daftar Supplier'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Evaluasi'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Kuesioner Keamanan'!$A$4:$E$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Kuesioner Keamanan'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -183,7 +187,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -346,6 +350,33 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -747,8 +778,15 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="28">
-      <c r="A4" s="31" t="inlineStr">
+    <row r="3" s="28">
+      <c r="A3" s="55" t="n"/>
+      <c r="B3" s="55" t="n"/>
+      <c r="C3" s="55" t="n"/>
+      <c r="D3" s="55" t="n"/>
+      <c r="E3" s="55" t="n"/>
+    </row>
+    <row r="4" ht="16.5" customHeight="1" s="28">
+      <c r="A4" s="56" t="inlineStr">
         <is>
           <t>Nomor dokumen</t>
         </is>
@@ -758,9 +796,12 @@
           <t>SNX-ISMS-FRM-03</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="28">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="C4" s="55" t="n"/>
+      <c r="D4" s="55" t="n"/>
+      <c r="E4" s="55" t="n"/>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" s="28">
+      <c r="A5" s="56" t="inlineStr">
         <is>
           <t>Judul</t>
         </is>
@@ -770,9 +811,12 @@
           <t>Supplier Technical &amp; Security Evaluation Records</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="28">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="C5" s="55" t="n"/>
+      <c r="D5" s="55" t="n"/>
+      <c r="E5" s="55" t="n"/>
+    </row>
+    <row r="6" ht="16.5" customHeight="1" s="28">
+      <c r="A6" s="56" t="inlineStr">
         <is>
           <t>Revisi</t>
         </is>
@@ -782,9 +826,12 @@
           <t>00 (Draft)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="28">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="C6" s="55" t="n"/>
+      <c r="D6" s="55" t="n"/>
+      <c r="E6" s="55" t="n"/>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" s="28">
+      <c r="A7" s="56" t="inlineStr">
         <is>
           <t>Tanggal draft</t>
         </is>
@@ -794,9 +841,12 @@
           <t>13 Oktober 2026</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="28">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="C7" s="55" t="n"/>
+      <c r="D7" s="55" t="n"/>
+      <c r="E7" s="55" t="n"/>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" s="28">
+      <c r="A8" s="56" t="inlineStr">
         <is>
           <t>Tanggal efektif</t>
         </is>
@@ -806,9 +856,12 @@
           <t>Ditetapkan saat pengesahan</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="28">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="C8" s="55" t="n"/>
+      <c r="D8" s="55" t="n"/>
+      <c r="E8" s="55" t="n"/>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" s="28">
+      <c r="A9" s="56" t="inlineStr">
         <is>
           <t>Klasifikasi</t>
         </is>
@@ -818,9 +871,12 @@
           <t>RESTRICTED (Internal)</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="28">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="C9" s="55" t="n"/>
+      <c r="D9" s="55" t="n"/>
+      <c r="E9" s="55" t="n"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="28">
+      <c r="A10" s="56" t="inlineStr">
         <is>
           <t>Pemilik dokumen</t>
         </is>
@@ -830,9 +886,12 @@
           <t>Head of Operation</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="28">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="C10" s="55" t="n"/>
+      <c r="D10" s="55" t="n"/>
+      <c r="E10" s="55" t="n"/>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="28">
+      <c r="A11" s="56" t="inlineStr">
         <is>
           <t>Disetujui oleh</t>
         </is>
@@ -842,9 +901,12 @@
           <t>Samuel Kristanto Utomo / President Director</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="28">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="C11" s="55" t="n"/>
+      <c r="D11" s="55" t="n"/>
+      <c r="E11" s="55" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="28">
+      <c r="A12" s="56" t="inlineStr">
         <is>
           <t>Acuan ISO 9001:2015</t>
         </is>
@@ -854,9 +916,12 @@
           <t>Klausul 8.4</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="28">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="C12" s="55" t="n"/>
+      <c r="D12" s="55" t="n"/>
+      <c r="E12" s="55" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1" s="28">
+      <c r="A13" s="56" t="inlineStr">
         <is>
           <t>Acuan ISO/IEC 27001:2022</t>
         </is>
@@ -866,9 +931,12 @@
           <t>Kontrol Annex A 5.19, 5.20, 5.21, 5.22, 5.23</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="28">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="C13" s="55" t="n"/>
+      <c r="D13" s="55" t="n"/>
+      <c r="E13" s="55" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1" s="28">
+      <c r="A14" s="56" t="inlineStr">
         <is>
           <t>Masa simpan record</t>
         </is>
@@ -878,64 +946,90 @@
           <t>Durasi kontrak + 3 tahun</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="23.85" customHeight="1" s="28">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="C14" s="55" t="n"/>
+      <c r="D14" s="55" t="n"/>
+      <c r="E14" s="55" t="n"/>
+    </row>
+    <row r="15" ht="43.5" customHeight="1" s="28">
+      <c r="A15" s="56" t="inlineStr">
         <is>
           <t>Tujuan</t>
         </is>
       </c>
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>Daftar supplier teknis, evaluasi kinerja dan keamanan informasi berkala, serta kuesioner keamanan supplier (A 5.19 sampai 5.23, ISO 9001 klausul 8.4).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="28">
-      <c r="A17" s="33" t="inlineStr">
+          <t>Mencatat supplier teknis, evaluasi berkala atas kinerja dan keamanan informasinya, serta kuesioner keamanan supplier (Annex A 5.19 sampai 5.23, ISO 9001 klausul 8.4).</t>
+        </is>
+      </c>
+      <c r="C15" s="55" t="n"/>
+      <c r="D15" s="55" t="n"/>
+      <c r="E15" s="55" t="n"/>
+    </row>
+    <row r="16" s="28">
+      <c r="A16" s="55" t="n"/>
+      <c r="B16" s="55" t="n"/>
+      <c r="C16" s="55" t="n"/>
+      <c r="D16" s="55" t="n"/>
+      <c r="E16" s="55" t="n"/>
+    </row>
+    <row r="17" ht="16.5" customHeight="1" s="28">
+      <c r="A17" s="57" t="inlineStr">
         <is>
           <t>Cara pakai</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="23.85" customHeight="1" s="28">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="B17" s="55" t="n"/>
+      <c r="C17" s="55" t="n"/>
+      <c r="D17" s="55" t="n"/>
+      <c r="E17" s="55" t="n"/>
+    </row>
+    <row r="18" ht="43.5" customHeight="1" s="28">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Daftarkan setiap supplier yang menopang layanan atau memegang akses atau data di sheet Daftar Supplier, berkoordinasi dengan Commercial dan Legal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="23.85" customHeight="1" s="28">
-      <c r="A19" s="34" t="inlineStr">
+          <t>Daftarkan di sheet Daftar Supplier setiap supplier yang menopang layanan atau memegang akses maupun data. Koordinasikan pendaftarannya dengan Commercial dan Legal.</t>
+        </is>
+      </c>
+      <c r="C18" s="55" t="n"/>
+      <c r="D18" s="55" t="n"/>
+      <c r="E18" s="55" t="n"/>
+    </row>
+    <row r="19" ht="43.5" customHeight="1" s="28">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Evaluasi supplier berkritikalitas Tinggi setiap semester, Sedang dan Rendah setiap tahun; jadwal berikutnya dihitung otomatis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="23.85" customHeight="1" s="28">
-      <c r="A20" s="34" t="inlineStr">
+          <t>Evaluasi supplier berkritikalitas Tinggi setiap semester, sedangkan supplier berkritikalitas Sedang dan Rendah setiap tahun. Jadwal evaluasi berikutnya terisi otomatis.</t>
+        </is>
+      </c>
+      <c r="C19" s="55" t="n"/>
+      <c r="D19" s="55" t="n"/>
+      <c r="E19" s="55" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1" s="28">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Isi skor 1 sampai 5 per kriteria di sheet Evaluasi; nilai tertimbang dan keputusan dihitung otomatis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="28">
-      <c r="A21" s="34" t="inlineStr">
+          <t>Isi skor 1 sampai 5 untuk setiap kriteria di sheet Evaluasi. Nilai tertimbang dan keputusan terisi otomatis.</t>
+        </is>
+      </c>
+      <c r="C20" s="55" t="n"/>
+      <c r="D20" s="55" t="n"/>
+      <c r="E20" s="55" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1" s="28">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
@@ -945,85 +1039,122 @@
           <t>Gunakan sheet Kuesioner Keamanan untuk supplier baru dan supplier berakses data.</t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="23.85" customHeight="1" s="28">
-      <c r="A22" s="34" t="inlineStr">
+      <c r="C21" s="55" t="n"/>
+      <c r="D21" s="55" t="n"/>
+      <c r="E21" s="55" t="n"/>
+    </row>
+    <row r="22" ht="30" customHeight="1" s="28">
+      <c r="A22" s="35" t="inlineStr">
         <is>
           <t>5.</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Breach SLA yang disebabkan supplier (SNX-OPS-SOP-05) menjadi masukan kriteria kinerja.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="28">
-      <c r="A24" s="33" t="inlineStr">
+          <t>Gunakan data breach SLA yang disebabkan supplier (SNX-OPS-SOP-05) sebagai masukan kriteria kinerja.</t>
+        </is>
+      </c>
+      <c r="C22" s="55" t="n"/>
+      <c r="D22" s="55" t="n"/>
+      <c r="E22" s="55" t="n"/>
+    </row>
+    <row r="23" s="28">
+      <c r="A23" s="55" t="n"/>
+      <c r="B23" s="55" t="n"/>
+      <c r="C23" s="55" t="n"/>
+      <c r="D23" s="55" t="n"/>
+      <c r="E23" s="55" t="n"/>
+    </row>
+    <row r="24" ht="16.5" customHeight="1" s="28">
+      <c r="A24" s="57" t="inlineStr">
         <is>
           <t>Legenda warna</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="28">
-      <c r="A25" s="36" t="n"/>
-      <c r="B25" s="34" t="inlineStr">
+      <c r="B24" s="55" t="n"/>
+      <c r="C24" s="55" t="n"/>
+      <c r="D24" s="55" t="n"/>
+      <c r="E24" s="55" t="n"/>
+    </row>
+    <row r="25" ht="16.5" customHeight="1" s="28">
+      <c r="A25" s="58" t="n"/>
+      <c r="B25" s="35" t="inlineStr">
         <is>
           <t>Sel input: diisi pengguna</t>
         </is>
       </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="28">
-      <c r="A26" s="37" t="n"/>
-      <c r="B26" s="34" t="inlineStr">
+      <c r="C25" s="55" t="n"/>
+      <c r="D25" s="55" t="n"/>
+      <c r="E25" s="55" t="n"/>
+    </row>
+    <row r="26" ht="43.5" customHeight="1" s="28">
+      <c r="A26" s="59" t="n"/>
+      <c r="B26" s="35" t="inlineStr">
         <is>
           <t>Biru muda: supplier yang sudah teridentifikasi; kontrak, NDA, dan sertifikasinya diverifikasi dengan Commercial dan Legal</t>
         </is>
       </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="28">
-      <c r="A27" s="38" t="n"/>
-      <c r="B27" s="34" t="inlineStr">
+      <c r="C26" s="55" t="n"/>
+      <c r="D26" s="55" t="n"/>
+      <c r="E26" s="55" t="n"/>
+    </row>
+    <row r="27" ht="16.5" customHeight="1" s="28">
+      <c r="A27" s="60" t="n"/>
+      <c r="B27" s="35" t="inlineStr">
         <is>
           <t>Sel rumus: jangan diubah</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="28">
-      <c r="A29" s="33" t="inlineStr">
+      <c r="C27" s="55" t="n"/>
+      <c r="D27" s="55" t="n"/>
+      <c r="E27" s="55" t="n"/>
+    </row>
+    <row r="28" s="28">
+      <c r="A28" s="55" t="n"/>
+      <c r="B28" s="55" t="n"/>
+      <c r="C28" s="55" t="n"/>
+      <c r="D28" s="55" t="n"/>
+      <c r="E28" s="55" t="n"/>
+    </row>
+    <row r="29" ht="16.5" customHeight="1" s="28">
+      <c r="A29" s="57" t="inlineStr">
         <is>
           <t>Riwayat revisi</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="28">
-      <c r="A30" s="39" t="inlineStr">
+      <c r="B29" s="55" t="n"/>
+      <c r="C29" s="55" t="n"/>
+      <c r="D29" s="55" t="n"/>
+      <c r="E29" s="55" t="n"/>
+    </row>
+    <row r="30" ht="16.5" customHeight="1" s="28">
+      <c r="A30" s="43" t="inlineStr">
         <is>
           <t>Revisi</t>
         </is>
       </c>
-      <c r="B30" s="39" t="inlineStr">
+      <c r="B30" s="43" t="inlineStr">
         <is>
           <t>Tanggal</t>
         </is>
       </c>
-      <c r="C30" s="39" t="inlineStr">
+      <c r="C30" s="43" t="inlineStr">
         <is>
           <t>Uraian perubahan</t>
         </is>
       </c>
-      <c r="D30" s="39" t="inlineStr">
+      <c r="D30" s="43" t="inlineStr">
         <is>
           <t>Disusun</t>
         </is>
       </c>
-      <c r="E30" s="39" t="inlineStr">
+      <c r="E30" s="43" t="inlineStr">
         <is>
           <t>Disetujui</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="23.85" customHeight="1" s="28">
+    <row r="31" ht="30" customHeight="1" s="28">
       <c r="A31" s="32" t="inlineStr">
         <is>
           <t>00</t>
@@ -1057,76 +1188,91 @@
       <c r="D32" s="32" t="n"/>
       <c r="E32" s="32" t="n"/>
     </row>
-    <row r="34" ht="15" customHeight="1" s="28">
-      <c r="A34" s="33" t="inlineStr">
+    <row r="33" s="28">
+      <c r="A33" s="55" t="n"/>
+      <c r="B33" s="55" t="n"/>
+      <c r="C33" s="55" t="n"/>
+      <c r="D33" s="55" t="n"/>
+      <c r="E33" s="55" t="n"/>
+    </row>
+    <row r="34" ht="16.5" customHeight="1" s="28">
+      <c r="A34" s="57" t="inlineStr">
         <is>
           <t>Pengesahan</t>
         </is>
       </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="28">
-      <c r="A35" s="39" t="inlineStr">
+      <c r="B34" s="55" t="n"/>
+      <c r="C34" s="55" t="n"/>
+      <c r="D34" s="55" t="n"/>
+      <c r="E34" s="55" t="n"/>
+    </row>
+    <row r="35" ht="16.5" customHeight="1" s="28">
+      <c r="A35" s="43" t="inlineStr">
         <is>
           <t>Peran</t>
         </is>
       </c>
-      <c r="B35" s="39" t="inlineStr">
+      <c r="B35" s="43" t="inlineStr">
         <is>
           <t>Nama dan jabatan</t>
         </is>
       </c>
-      <c r="C35" s="39" t="inlineStr">
+      <c r="C35" s="43" t="inlineStr">
         <is>
           <t>Tanda tangan</t>
         </is>
       </c>
-      <c r="D35" s="39" t="inlineStr">
+      <c r="D35" s="43" t="inlineStr">
         <is>
           <t>Tanggal</t>
         </is>
       </c>
+      <c r="E35" s="55" t="n"/>
     </row>
     <row r="36" ht="27.75" customHeight="1" s="28">
-      <c r="A36" s="40" t="inlineStr">
+      <c r="A36" s="32" t="inlineStr">
         <is>
           <t>Disusun oleh</t>
         </is>
       </c>
-      <c r="B36" s="40" t="inlineStr">
+      <c r="B36" s="32" t="inlineStr">
         <is>
           <t>Erik Dwi Yanto / Technical/Operation Engineer L1</t>
         </is>
       </c>
-      <c r="C36" s="40" t="n"/>
-      <c r="D36" s="40" t="n"/>
+      <c r="C36" s="32" t="n"/>
+      <c r="D36" s="32" t="n"/>
+      <c r="E36" s="55" t="n"/>
     </row>
     <row r="37" ht="27.75" customHeight="1" s="28">
-      <c r="A37" s="40" t="inlineStr">
+      <c r="A37" s="32" t="inlineStr">
         <is>
           <t>Diperiksa oleh</t>
         </is>
       </c>
-      <c r="B37" s="40" t="inlineStr">
+      <c r="B37" s="32" t="inlineStr">
         <is>
           <t>Fani Fatullah / VP Tech Operation and Services</t>
         </is>
       </c>
-      <c r="C37" s="40" t="n"/>
-      <c r="D37" s="40" t="n"/>
+      <c r="C37" s="32" t="n"/>
+      <c r="D37" s="32" t="n"/>
+      <c r="E37" s="55" t="n"/>
     </row>
     <row r="38" ht="27.75" customHeight="1" s="28">
-      <c r="A38" s="40" t="inlineStr">
+      <c r="A38" s="32" t="inlineStr">
         <is>
           <t>Disetujui oleh</t>
         </is>
       </c>
-      <c r="B38" s="40" t="inlineStr">
+      <c r="B38" s="32" t="inlineStr">
         <is>
           <t>Samuel Kristanto Utomo / President Director</t>
         </is>
       </c>
-      <c r="C38" s="40" t="n"/>
-      <c r="D38" s="40" t="n"/>
+      <c r="C38" s="32" t="n"/>
+      <c r="D38" s="32" t="n"/>
+      <c r="E38" s="55" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -1170,151 +1316,167 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="28" customWidth="1" style="27" min="1" max="1"/>
-    <col width="16" customWidth="1" style="27" min="2" max="2"/>
+    <col width="18" customWidth="1" style="27" min="2" max="2"/>
     <col width="17" customWidth="1" style="27" min="3" max="3"/>
     <col width="16" customWidth="1" style="27" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="28">
-      <c r="A1" s="42" t="inlineStr">
+    <row r="1" ht="16.5" customHeight="1" s="28">
+      <c r="A1" s="61" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
       </c>
-      <c r="B1" s="42" t="inlineStr">
+      <c r="B1" s="61" t="inlineStr">
         <is>
           <t>Kritikalitas</t>
         </is>
       </c>
-      <c r="C1" s="42" t="inlineStr">
+      <c r="C1" s="61" t="inlineStr">
         <is>
           <t>YaTidak</t>
         </is>
       </c>
-      <c r="D1" s="42" t="inlineStr">
+      <c r="D1" s="61" t="inlineStr">
         <is>
           <t>Skor</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="28">
-      <c r="A2" s="34" t="inlineStr">
+    <row r="2" ht="30" customHeight="1" s="28">
+      <c r="A2" s="62" t="inlineStr">
         <is>
           <t>Infrastruktur cloud dan DC</t>
         </is>
       </c>
-      <c r="B2" s="34" t="inlineStr">
+      <c r="B2" s="62" t="inlineStr">
         <is>
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="C2" s="34" t="inlineStr">
+      <c r="C2" s="62" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="D2" s="34" t="n">
+      <c r="D2" s="62" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="28">
-      <c r="A3" s="34" t="inlineStr">
+    <row r="3" ht="16.5" customHeight="1" s="28">
+      <c r="A3" s="62" t="inlineStr">
         <is>
           <t>Partner SOC</t>
         </is>
       </c>
-      <c r="B3" s="34" t="inlineStr">
+      <c r="B3" s="62" t="inlineStr">
         <is>
           <t>Sedang</t>
         </is>
       </c>
-      <c r="C3" s="34" t="inlineStr">
+      <c r="C3" s="62" t="inlineStr">
         <is>
           <t>Tidak</t>
         </is>
       </c>
-      <c r="D3" s="34" t="n">
+      <c r="D3" s="62" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="28">
-      <c r="A4" s="34" t="inlineStr">
+    <row r="4" ht="30" customHeight="1" s="28">
+      <c r="A4" s="62" t="inlineStr">
         <is>
           <t>Platform observability</t>
         </is>
       </c>
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="62" t="inlineStr">
         <is>
           <t>Rendah</t>
         </is>
       </c>
-      <c r="C4" s="34" t="inlineStr">
+      <c r="C4" s="62" t="inlineStr">
         <is>
           <t>Belum diketahui</t>
         </is>
       </c>
-      <c r="D4" s="34" t="n">
+      <c r="D4" s="62" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="28">
-      <c r="A5" s="34" t="inlineStr">
+    <row r="5" ht="16.5" customHeight="1" s="28">
+      <c r="A5" s="62" t="inlineStr">
         <is>
           <t>Keamanan dan CDN</t>
         </is>
       </c>
-      <c r="D5" s="34" t="n">
+      <c r="B5" s="63" t="n"/>
+      <c r="C5" s="63" t="n"/>
+      <c r="D5" s="62" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="28">
-      <c r="A6" s="34" t="inlineStr">
+    <row r="6" ht="16.5" customHeight="1" s="28">
+      <c r="A6" s="62" t="inlineStr">
         <is>
           <t>Backup</t>
         </is>
       </c>
-      <c r="D6" s="34" t="n">
+      <c r="B6" s="63" t="n"/>
+      <c r="C6" s="63" t="n"/>
+      <c r="D6" s="62" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="28">
-      <c r="A7" s="34" t="inlineStr">
+    <row r="7" ht="16.5" customHeight="1" s="28">
+      <c r="A7" s="62" t="inlineStr">
         <is>
           <t>Lisensi software</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="28">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="B7" s="63" t="n"/>
+      <c r="C7" s="63" t="n"/>
+      <c r="D7" s="63" t="n"/>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" s="28">
+      <c r="A8" s="62" t="inlineStr">
         <is>
           <t>Sertifikat SSL</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="28">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="B8" s="63" t="n"/>
+      <c r="C8" s="63" t="n"/>
+      <c r="D8" s="63" t="n"/>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" s="28">
+      <c r="A9" s="62" t="inlineStr">
         <is>
           <t>SaaS kolaborasi</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="28">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="B9" s="63" t="n"/>
+      <c r="C9" s="63" t="n"/>
+      <c r="D9" s="63" t="n"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="28">
+      <c r="A10" s="62" t="inlineStr">
         <is>
           <t>Lainnya</t>
         </is>
       </c>
+      <c r="B10" s="63" t="n"/>
+      <c r="C10" s="63" t="n"/>
+      <c r="D10" s="63" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -1331,10 +1493,13 @@
     <col width="32" customWidth="1" style="27" min="2" max="2"/>
     <col width="30" customWidth="1" style="27" min="3" max="3"/>
     <col width="18" customWidth="1" style="27" min="4" max="4"/>
-    <col width="10" customWidth="1" style="27" min="5" max="6"/>
-    <col width="14" customWidth="1" style="27" min="7" max="8"/>
+    <col width="18" customWidth="1" style="27" min="5" max="6"/>
+    <col width="13" customWidth="1" style="28" min="6" max="6"/>
+    <col width="17" customWidth="1" style="27" min="7" max="8"/>
+    <col width="13" customWidth="1" style="28" min="8" max="8"/>
     <col width="16" customWidth="1" style="27" min="9" max="9"/>
-    <col width="11" customWidth="1" style="27" min="10" max="11"/>
+    <col width="12" customWidth="1" style="27" min="10" max="11"/>
+    <col width="15" customWidth="1" style="28" min="11" max="11"/>
     <col width="26" customWidth="1" style="27" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -1352,7 +1517,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="31.5" customHeight="1" s="28">
+    <row r="4" ht="70.5" customHeight="1" s="28">
       <c r="A4" s="43" t="inlineStr">
         <is>
           <t>ID</t>
@@ -1414,7 +1579,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="23.85" customHeight="1" s="28">
+    <row r="5" ht="43.5" customHeight="1" s="28">
       <c r="A5" s="44" t="inlineStr">
         <is>
           <t>SUP-001</t>
@@ -1471,7 +1636,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="23.85" customHeight="1" s="28">
+    <row r="6" ht="30" customHeight="1" s="28">
       <c r="A6" s="44" t="inlineStr">
         <is>
           <t>SUP-002</t>
@@ -1524,7 +1689,7 @@
       </c>
       <c r="L6" s="44" t="n"/>
     </row>
-    <row r="7" ht="23.85" customHeight="1" s="28">
+    <row r="7" ht="30" customHeight="1" s="28">
       <c r="A7" s="44" t="inlineStr">
         <is>
           <t>SUP-003</t>
@@ -1577,7 +1742,7 @@
       </c>
       <c r="L7" s="44" t="n"/>
     </row>
-    <row r="8" ht="23.85" customHeight="1" s="28">
+    <row r="8" ht="30" customHeight="1" s="28">
       <c r="A8" s="44" t="inlineStr">
         <is>
           <t>SUP-004</t>
@@ -1630,7 +1795,7 @@
       </c>
       <c r="L8" s="44" t="n"/>
     </row>
-    <row r="9" ht="23.85" customHeight="1" s="28">
+    <row r="9" ht="30" customHeight="1" s="28">
       <c r="A9" s="44" t="inlineStr">
         <is>
           <t>SUP-005</t>
@@ -1683,7 +1848,7 @@
       </c>
       <c r="L9" s="44" t="n"/>
     </row>
-    <row r="10" ht="23.85" customHeight="1" s="28">
+    <row r="10" ht="30" customHeight="1" s="28">
       <c r="A10" s="44" t="inlineStr">
         <is>
           <t>SUP-006</t>
@@ -1736,7 +1901,7 @@
       </c>
       <c r="L10" s="44" t="n"/>
     </row>
-    <row r="11" ht="23.85" customHeight="1" s="28">
+    <row r="11" ht="30" customHeight="1" s="28">
       <c r="A11" s="44" t="inlineStr">
         <is>
           <t>SUP-007</t>
@@ -1789,7 +1954,7 @@
       </c>
       <c r="L11" s="44" t="n"/>
     </row>
-    <row r="12" ht="23.85" customHeight="1" s="28">
+    <row r="12" ht="30" customHeight="1" s="28">
       <c r="A12" s="44" t="inlineStr">
         <is>
           <t>SUP-008</t>
@@ -2569,19 +2734,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N104"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="10" customWidth="1" style="27" min="1" max="1"/>
-    <col width="9" customWidth="1" style="27" min="2" max="2"/>
+    <col width="11" customWidth="1" style="27" min="1" max="1"/>
+    <col width="12" customWidth="1" style="27" min="2" max="2"/>
     <col width="26" customWidth="1" style="27" min="3" max="3"/>
-    <col width="12" customWidth="1" style="27" min="4" max="9"/>
+    <col width="18" customWidth="1" style="27" min="4" max="9"/>
+    <col width="20" customWidth="1" style="28" min="5" max="5"/>
+    <col width="14" customWidth="1" style="28" min="6" max="6"/>
+    <col width="17" customWidth="1" style="28" min="7" max="7"/>
+    <col width="13" customWidth="1" style="28" min="8" max="8"/>
+    <col width="20" customWidth="1" style="28" min="9" max="9"/>
     <col width="8" customWidth="1" style="27" min="10" max="10"/>
     <col width="14" customWidth="1" style="27" min="11" max="11"/>
     <col width="26" customWidth="1" style="27" min="12" max="12"/>
     <col width="14" customWidth="1" style="27" min="13" max="14"/>
+    <col width="14" customWidth="1" style="28" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.15" customHeight="1" s="28">
@@ -2623,7 +2794,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1" s="28">
+    <row r="4" ht="111" customHeight="1" s="28">
       <c r="A4" s="43" t="inlineStr">
         <is>
           <t>Periode</t>
@@ -5215,7 +5386,7 @@
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -5245,7 +5416,7 @@
     <row r="2" ht="15" customHeight="1" s="28">
       <c r="A2" s="30" t="inlineStr">
         <is>
-          <t>Satu set jawaban per supplier; salin sheet ini bila perlu. Penilaian dipakai untuk kriteria Kontrol keamanan informasi pada sheet Evaluasi.</t>
+          <t>Gunakan satu set jawaban untuk satu supplier, dan salin sheet ini jika perlu. Hasilnya dipakai untuk kriteria Kontrol keamanan informasi di sheet Evaluasi.</t>
         </is>
       </c>
     </row>
@@ -5257,7 +5428,7 @@
       </c>
       <c r="E3" s="54" t="n"/>
     </row>
-    <row r="4" ht="31.5" customHeight="1" s="28">
+    <row r="4" ht="70.5" customHeight="1" s="28">
       <c r="A4" s="43" t="inlineStr">
         <is>
           <t>No</t>
@@ -5284,7 +5455,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="23.85" customHeight="1" s="28">
+    <row r="5" ht="43.5" customHeight="1" s="28">
       <c r="A5" s="44" t="n">
         <v>1</v>
       </c>
@@ -5297,7 +5468,7 @@
       <c r="D5" s="47" t="n"/>
       <c r="E5" s="47" t="n"/>
     </row>
-    <row r="6" ht="15" customHeight="1" s="28">
+    <row r="6" ht="30" customHeight="1" s="28">
       <c r="A6" s="44" t="n">
         <v>2</v>
       </c>
@@ -5310,7 +5481,7 @@
       <c r="D6" s="47" t="n"/>
       <c r="E6" s="47" t="n"/>
     </row>
-    <row r="7" ht="23.85" customHeight="1" s="28">
+    <row r="7" ht="30" customHeight="1" s="28">
       <c r="A7" s="44" t="n">
         <v>3</v>
       </c>
@@ -5323,7 +5494,7 @@
       <c r="D7" s="47" t="n"/>
       <c r="E7" s="47" t="n"/>
     </row>
-    <row r="8" ht="23.85" customHeight="1" s="28">
+    <row r="8" ht="30" customHeight="1" s="28">
       <c r="A8" s="44" t="n">
         <v>4</v>
       </c>
@@ -5336,7 +5507,7 @@
       <c r="D8" s="47" t="n"/>
       <c r="E8" s="47" t="n"/>
     </row>
-    <row r="9" ht="15" customHeight="1" s="28">
+    <row r="9" ht="30" customHeight="1" s="28">
       <c r="A9" s="44" t="n">
         <v>5</v>
       </c>
@@ -5349,7 +5520,7 @@
       <c r="D9" s="47" t="n"/>
       <c r="E9" s="47" t="n"/>
     </row>
-    <row r="10" ht="23.85" customHeight="1" s="28">
+    <row r="10" ht="30" customHeight="1" s="28">
       <c r="A10" s="44" t="n">
         <v>6</v>
       </c>
@@ -5362,7 +5533,7 @@
       <c r="D10" s="47" t="n"/>
       <c r="E10" s="47" t="n"/>
     </row>
-    <row r="11" ht="23.85" customHeight="1" s="28">
+    <row r="11" ht="30" customHeight="1" s="28">
       <c r="A11" s="44" t="n">
         <v>7</v>
       </c>
@@ -5375,7 +5546,7 @@
       <c r="D11" s="47" t="n"/>
       <c r="E11" s="47" t="n"/>
     </row>
-    <row r="12" ht="15" customHeight="1" s="28">
+    <row r="12" ht="30" customHeight="1" s="28">
       <c r="A12" s="44" t="n">
         <v>8</v>
       </c>
@@ -5388,7 +5559,7 @@
       <c r="D12" s="47" t="n"/>
       <c r="E12" s="47" t="n"/>
     </row>
-    <row r="13" ht="15" customHeight="1" s="28">
+    <row r="13" ht="30" customHeight="1" s="28">
       <c r="A13" s="44" t="n">
         <v>9</v>
       </c>
@@ -5401,7 +5572,7 @@
       <c r="D13" s="47" t="n"/>
       <c r="E13" s="47" t="n"/>
     </row>
-    <row r="14" ht="15" customHeight="1" s="28">
+    <row r="14" ht="30" customHeight="1" s="28">
       <c r="A14" s="44" t="n">
         <v>10</v>
       </c>
@@ -5414,7 +5585,7 @@
       <c r="D14" s="47" t="n"/>
       <c r="E14" s="47" t="n"/>
     </row>
-    <row r="15" ht="15" customHeight="1" s="28">
+    <row r="15" ht="30" customHeight="1" s="28">
       <c r="A15" s="44" t="n">
         <v>11</v>
       </c>
@@ -5427,7 +5598,7 @@
       <c r="D15" s="47" t="n"/>
       <c r="E15" s="47" t="n"/>
     </row>
-    <row r="16" ht="15" customHeight="1" s="28">
+    <row r="16" ht="16.5" customHeight="1" s="28">
       <c r="A16" s="44" t="n">
         <v>12</v>
       </c>
